--- a/原始資料/一無王開叫.xlsx
+++ b/原始資料/一無王開叫.xlsx
@@ -603,15 +603,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>★ 開叫點力三段</t>
+          <t>★ 開叫點力</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>本體系的 1NT 點力**依局況與座位而變**，這是讀本章最先要記住的事：
-· 無局、第1／2家 → 10-12點（弱無將）
-· 無局、第3／4家 → 13-15點
-· 有局，任何位置 → 14-16點</t>
+          <t>**家規：1NT 開叫一律 10-12 點，不分座位、不分局況。**
+原書為三段制（無局第1／2家 10-12／無局第3／4家 13-15／有局 14-16），本檔已全部改為 10-12。
+配合家規的開叫階梯：均型牌 10-12 → 1NT；13-14 → 1♦；15以上 → 1♣。三段接續、無缺口也無重疊。</t>
         </is>
       </c>
     </row>
@@ -930,7 +929,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>1NT = 無局第1／2家 10-12點｜無局第3／4家 13-15點｜有局 14-16點</t>
+          <t>1NT = 10-12 點（家規：不分座位與局況一律 10-12；原書為 10-12／13-15／14-16 三段制）</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1043,12 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>對 10-12 點的弱無將是阻擊叫，表示 5-5 高花；對 14-16 點的強無將則是邀叫。</t>
+          <t>阻擊叫，表示 5-5 高花。（原書另有一支：對 14-16 點的強無將是邀叫——家規下 1NT 一律 10-12，該支不再適用）</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>依開叫點力而定</t>
+          <t>阻擊</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1060,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>對 10-12 點的弱無將是阻擊叫，表示 5-5 低花；對 14-16 點的強無將則是逼叫。（在 3♠ 後再叫 4♥ 是 Sidestep，4♣／4♦ 則是滿貫興趣）</t>
+          <t>阻擊叫，表示 5-5 低花。（原書另有一支：對 14-16 點的強無將是逼叫，在 3♠ 後再叫 4♥ 是 Sidestep、4♣／4♦ 是滿貫興趣——家規下該支不再適用）</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>依開叫點力而定</t>
+          <t>阻擊</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2822,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>10-12點（無局第1／2家的弱無將）</t>
+          <t>10-12點</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3119,7 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>14-16點（有局的強無將）</t>
+          <t>14-16點　⚠ 原書範例：此為原書有局的強無將；家規下 1NT 一律 10-12，這手牌不會開 1NT</t>
         </is>
       </c>
     </row>

--- a/原始資料/一無王開叫.xlsx
+++ b/原始資料/一無王開叫.xlsx
@@ -14,8 +14,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.B分支(2♠)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.C分支(2NT)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.對1NT的防守" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.示例牌張" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.示例叫序" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -588,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -863,30 +862,6 @@
       <c r="B28" s="7" t="inlineStr">
         <is>
           <t>敵方開叫 1NT 時我方的爭叫體系與後續處理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>8. 示例牌張</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>例1–例3 的持牌、局況與結果評論。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>9. 示例叫序</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>例1–例3 的完整叫序，逐叫列出。</t>
         </is>
       </c>
     </row>
@@ -2314,1294 +2289,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="66" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>叫牌示例：持牌、局況與結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>例號</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>出處</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>局況／發牌</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>方位</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>♠</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>♥</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>♦</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>♣</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>最終定約</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>評論</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>1987年冰島公開雙人賽（對手為齊亞與 Jaggy Shivdasani）</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>雙無局，東發牌</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>A97542</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>AQJ10</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>6♠</t>
-        </is>
-      </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t>齊亞首攻小♣，Ulf 長考後用 10 飛成功。發現♠K也在齊亞手裡後席捲13墩。Glenn 在 4♠ 後叫 6♠ 是好定約——就算對方找到最有力的首攻（小♥）且♥K在Q後面，也只要飛中♠K就行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr"/>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>QJ103</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>A83</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>K1083</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr"/>
-      <c r="J5" s="14" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>東西有局，東發牌</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>AJ9862</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>AKJ</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>QJ</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>7NT</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>★ 脫離接力的示範。牌力介於成局與滿貫之間時，最好回到自然叫徵求同伴意見。Ulf 在 3♠ 後用最經濟的 4♣ 扣叫表示將牌支持＋高限，之後羅馬關鍵張、5NT 大滿貫邀叫一路推上去。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>KQ</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>A74</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>AK965</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr"/>
-      <c r="J7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>1997年百慕大杯半決賽 挪威對法國</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>雙方無局，南開叫</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>北</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>AKQ952</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>AK4</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>A104</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>6♥</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>★ 走 C 分支，四叫問完牌型。法國隊 Perron 首攻♠A——這是唯一能送成 6♥ 的首攻。教訓：對抗接力體系，最好不要首攻A，因為接力能查出每門花色的控制，防守方連續兌現兩墩的機會很少。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>西</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>A8765</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
-        <is>
-          <t>J9765</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>東</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>J1032</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>J862</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>KQ4</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>J64</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>Q32</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>Q975</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>叫牌示例：完整叫序（逐叫）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>例號</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>局況</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>叫者</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>叫品</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>雙無局，東發牌</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>1NT</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>10-12點</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機，逼局</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr"/>
-      <c r="C6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>2♠</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>4張♠，否認4張♥ → 進 B 分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr"/>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>接力</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr"/>
-      <c r="B8" s="12" t="inlineStr"/>
-      <c r="C8" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>3♦</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>4張♦</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr"/>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>3♥</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Sidestep</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr"/>
-      <c r="B10" s="12" t="inlineStr"/>
-      <c r="C10" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>3NT</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>4-3-4-2分佈</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="inlineStr"/>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>4♣</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>CRASH（問A）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr"/>
-      <c r="B12" s="12" t="inlineStr"/>
-      <c r="C12" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>4♦</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>一個A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>4♥</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>CRASH（問K）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr"/>
-      <c r="B14" s="12" t="inlineStr"/>
-      <c r="C14" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>4♠</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>一個K</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr"/>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>6♠</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>最佳定約</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr"/>
-      <c r="B16" s="12" t="inlineStr"/>
-      <c r="C16" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>註：3NT 那一叫是 Sidestep 的加2級：未知的兩門是♥（高）和♣（低），3(高)-2(低) → 4-3-4-2。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>東西有局，東發牌</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>1NT</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>14-16點　⚠ 原書範例：此為原書有局的強無將；家規下 1NT 一律 10-12，這手牌不會開 1NT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr"/>
-      <c r="B20" s="14" t="inlineStr"/>
-      <c r="C20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機，逼局</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>5-3-3-2牌型，5張套是♣</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr"/>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>3♠</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>自然叫，至少5張套 ← 脫離接力</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr"/>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>4♣</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>扣叫（最經濟的扣叫＝將牌有支持＋高限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr"/>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>4♥</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>扣叫</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr"/>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>4NT</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>羅馬關鍵張問叫</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr"/>
-      <c r="B26" s="14" t="inlineStr"/>
-      <c r="C26" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>5♥</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>兩個A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr"/>
-      <c r="B27" s="12" t="inlineStr"/>
-      <c r="C27" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>5NT</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>大滿貫邀叫（4個A在握，將牌無失張）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr"/>
-      <c r="B28" s="14" t="inlineStr"/>
-      <c r="C28" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>6♥</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>一個♥K，且有大滿貫興趣</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr"/>
-      <c r="B29" s="12" t="inlineStr"/>
-      <c r="C29" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>7♠</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>我的牌不能再好了</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr"/>
-      <c r="B30" s="14" t="inlineStr"/>
-      <c r="C30" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>7NT</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>和 7♠ 機會均等</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr"/>
-      <c r="B31" s="12" t="inlineStr"/>
-      <c r="C31" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>註：★ 牌力介於成局與滿貫之間時，接力問不出你要的東西——Glenn 手牌平均，需要知道同伴大牌的位置與高低限，所以在第二叫就脫離接力叫出自然的 3♠。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>雙方無局，南開叫（東西方未爭叫）</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>1NT</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>10-12點</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr"/>
-      <c r="B35" s="14" t="inlineStr"/>
-      <c r="C35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>北</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機，逼局</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr"/>
-      <c r="B36" s="12" t="inlineStr"/>
-      <c r="C36" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>沒有4張高花和5張低花 → 進 C 分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="24" t="inlineStr"/>
-      <c r="B37" s="14" t="inlineStr"/>
-      <c r="C37" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>北</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>接力</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="25" t="inlineStr"/>
-      <c r="B38" s="12" t="inlineStr"/>
-      <c r="C38" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>3NT</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>3-3-3-4分佈</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr"/>
-      <c r="B39" s="14" t="inlineStr"/>
-      <c r="C39" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>北</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>4♣</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr"/>
-      <c r="B40" s="12" t="inlineStr"/>
-      <c r="C40" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>4♥</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>沒有A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="24" t="inlineStr"/>
-      <c r="B41" s="14" t="inlineStr"/>
-      <c r="C41" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>北</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>6♥</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="inlineStr"/>
-      <c r="B42" s="12" t="inlineStr"/>
-      <c r="C42" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>南</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="26" t="inlineStr">
-        <is>
-          <t>註：★ 防守方的教訓：Perron 首攻♠A，這是唯一能送成 6♥ 的首攻。對抗接力體系最好不要首攻A。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A43:F43"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>